--- a/outputs/evaluation/requirement/design/v2/gemini-3-5-flash-lite/CF_M05/second/CF_M05_req_eval.xlsx
+++ b/outputs/evaluation/requirement/design/v2/gemini-3-5-flash-lite/CF_M05/second/CF_M05_req_eval.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,6 +529,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -546,6 +551,9 @@
         <v>0.9615</v>
       </c>
       <c r="D13" t="n">
+        <v>0.8621</v>
+      </c>
+      <c r="E13" t="n">
         <v>0.984</v>
       </c>
     </row>
@@ -755,10 +763,6 @@
           <t>Ensure that data from other clients cannot be accessed.</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>FR</t>
@@ -772,10 +776,6 @@
           <t>Ensure that other customers' data cannot be accessed.</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -806,10 +806,6 @@
           <t>Visualize the applications of the portal to which the user has access.</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>FR</t>
@@ -823,10 +819,6 @@
           <t>View the portal applications to which the user has access.</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -857,14 +849,11 @@
           <t>No user can access data from other clients.</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>R_31</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -878,14 +867,11 @@
           <t>No user can access data from other customers.</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>CF_M05_R24</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -921,9 +907,6 @@
           <t>C_09</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>QR</t>
@@ -947,8 +930,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -979,14 +960,11 @@
           <t>The learning time for the new functionalities should not exceed 5 minutes.</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>R_21</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1000,14 +978,11 @@
           <t>Learning time for new features should not exceed 5 min.</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>CF_M05_R14</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1038,10 +1013,6 @@
           <t>Restrict the visualization and actions (create, modify, and delete) on data according to the roles assigned to the user.</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1055,10 +1026,6 @@
           <t>Restrict actions (create, modify and delete) on data according to the roles assigned to the user.</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1089,10 +1056,6 @@
           <t>Access the portal through personal credential authentication.</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1106,10 +1069,6 @@
           <t>Access the portal using credential authentication personal.</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1145,9 +1104,6 @@
           <t>C_05</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1171,8 +1127,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1203,14 +1157,11 @@
           <t>The system availability must be a minimum of 99.9%, even during intensive use moments.</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>R_27</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1225,14 +1176,11 @@
 during times of intensive use.</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>CF_M05_R20</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1263,14 +1211,11 @@
           <t>The system availability must be a minimum of 99.9%, even during intensive use moments.</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>R_25</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1284,14 +1229,11 @@
           <t>System availability must be at least 99.9%, even during times of intensive use.</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>CF_M05_R18</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1322,10 +1264,6 @@
           <t>Grant or remove access to applications for users.</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1339,10 +1277,6 @@
           <t>Give or remove access to applications from users.</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1378,9 +1312,6 @@
           <t>C_01</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1404,8 +1335,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1436,14 +1365,11 @@
           <t>The system must feature a secure authentication and permission verification mechanism to ensure that each user can only access the information and functionalities corresponding to them.</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>R_29</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1457,14 +1383,11 @@
           <t>The system must have a secure authentication mechanism and permission verification to ensure that each user can only access the information and functionalities that correspond to it.</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>CF_M05_R22</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1495,14 +1418,11 @@
           <t>The design, colors, typographies, and organization must be consistent with the old version.</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>R_15</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1516,14 +1436,11 @@
           <t>The design, organization, colors and typoghraphy must be consistent with the old version.</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>CF_M05_R08</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1559,9 +1476,6 @@
           <t>C_08</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1586,8 +1500,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1618,14 +1530,11 @@
           <t>Response time must not exceed 1 second in 95% of queries.</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>R_23</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1639,14 +1548,11 @@
           <t>Response time should not exceed 1 second in 95% of queries.</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>CF_M05_R16</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1677,10 +1583,6 @@
           <t>Access the applications to which the user has access within the portal.</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1694,10 +1596,6 @@
           <t>Access the applications to which the user has access on the portal.</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1728,14 +1626,11 @@
           <t>80% of users do not need to ask for help from a third party to use the application.</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>R_17</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1750,14 +1645,11 @@
 use the application.</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>CF_M05_R10</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1793,9 +1685,6 @@
           <t>C_02</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1819,8 +1708,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1856,9 +1743,6 @@
           <t>C_06</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1883,8 +1767,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1920,9 +1802,6 @@
           <t>C_03</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1946,8 +1825,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1978,10 +1855,6 @@
           <t>Convert any mention of the old name to the new name.</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1995,10 +1868,6 @@
           <t>Convert any mention of the old name to the new name.</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2034,9 +1903,6 @@
           <t>C_07</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>QR</t>
@@ -2061,8 +1927,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2098,9 +1962,6 @@
           <t>C_04</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>QR</t>
@@ -2124,8 +1985,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2156,14 +2015,11 @@
           <t>Complete and correct translations in both languages.</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>R_19</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -2177,14 +2033,11 @@
           <t>Complete and correct translations in both languages.</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>CF_M05_R12</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
